--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260824.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260824.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>225,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1751,6 +1751,24 @@
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>RP_NTD</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>RP</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>4,979,461,838</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
